--- a/data-manipulation-scripts/sheets-cleanup/sheets/GRAXA 15_02.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/GRAXA 15_02.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
   <si>
     <t>CÓD. BARRA</t>
   </si>
@@ -31,7 +31,10 @@
     <t xml:space="preserve">GRAXA ADESIVA WURTH </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
+    <t>7891799529000</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GRAXA ADESIVA WMAX LUBRIFICANTE </t>
   </si>
 </sst>
 </file>
@@ -345,9 +348,15 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2">
+        <v>12.0</v>
+      </c>
+      <c r="D3" s="2">
+        <v>30.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1"/>
